--- a/sheets/대금율보/검수/진도아리랑 (b2_096_2).xlsx
+++ b/sheets/대금율보/검수/진도아리랑 (b2_096_2).xlsx
@@ -3709,8 +3709,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -3720,8 +3719,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3742,8 +3740,7 @@
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋㴌
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="I8" s="24" t="inlineStr">
@@ -3754,8 +3751,7 @@
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K8" s="24" t="inlineStr">
@@ -3765,8 +3761,7 @@
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M8" s="24" t="inlineStr">
@@ -4128,8 +4123,7 @@
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌淋
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="M14" s="24"/>

--- a/sheets/대금율보/검수/진도아리랑 (b2_096_2).xlsx
+++ b/sheets/대금율보/검수/진도아리랑 (b2_096_2).xlsx
@@ -3356,24 +3356,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="71.62" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="71.62" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="71.62" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="71.62" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="71.62" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="71.62" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="71.62" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="71.62" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="71.62" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="71.62" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="71.62" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="71.62" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4134,6 +4134,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>